--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457406</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457393</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457403</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457390</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457387</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1511,6 +1546,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457408</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1616,6 +1656,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129153890</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457416</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1840,6 +1890,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457418</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1972,6 +2027,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457385</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2091,6 +2151,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117018888</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2203,6 +2268,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457394</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2319,6 +2389,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457400</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2446,6 +2521,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457407</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2553,6 +2633,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457384</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2660,6 +2745,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457392</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2776,6 +2866,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457386</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2892,6 +2987,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457395</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2999,6 +3099,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457396</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3115,6 +3220,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457397</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3222,6 +3332,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457398</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3338,6 +3453,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457401</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3454,6 +3574,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457402</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3570,6 +3695,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457404</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3686,6 +3816,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457420</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3802,6 +3937,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457409</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3909,6 +4049,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457411</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4016,6 +4161,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457415</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4128,6 +4278,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457413</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4244,6 +4399,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457389</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4370,6 +4530,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457412</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4477,8 +4642,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457414</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Joakim Mårts</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3703,37 +3703,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134457409</v>
+        <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>106324</v>
+        <v>99274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602380</v>
+        <v>602403</v>
       </c>
       <c r="R27" t="n">
-        <v>6634441</v>
+        <v>6634688</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3812,57 +3812,66 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Joakim Mårts</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134457409</t>
+          <t>https://artportalen.se/Sighting/134457420</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134457411</v>
+        <v>134457409</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>106324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dragmansbo, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602465</v>
+        <v>602380</v>
       </c>
       <c r="R28" t="n">
-        <v>6634498</v>
+        <v>6634441</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3894,7 +3903,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3904,7 +3913,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3930,13 +3939,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134457411</t>
+          <t>https://artportalen.se/Sighting/134457409</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134457415</v>
+        <v>134457411</v>
       </c>
       <c r="B29" t="n">
         <v>91974</v>
@@ -3971,10 +3980,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602577</v>
+        <v>602465</v>
       </c>
       <c r="R29" t="n">
-        <v>6634728</v>
+        <v>6634498</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4006,7 +4015,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4016,7 +4025,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4042,56 +4051,51 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134457415</t>
+          <t>https://artportalen.se/Sighting/134457411</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134457413</v>
+        <v>134457415</v>
       </c>
       <c r="B30" t="n">
-        <v>57972</v>
+        <v>91974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dragmansbo, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602589</v>
+        <v>602577</v>
       </c>
       <c r="R30" t="n">
-        <v>6634549</v>
+        <v>6634728</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4123,7 +4127,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4133,7 +4137,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4159,48 +4163,44 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134457413</t>
+          <t>https://artportalen.se/Sighting/134457415</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134457389</v>
+        <v>134457413</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602427</v>
+        <v>602589</v>
       </c>
       <c r="R31" t="n">
-        <v>6634739</v>
+        <v>6634549</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4280,13 +4280,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134457389</t>
+          <t>https://artportalen.se/Sighting/134457413</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134457412</v>
+        <v>134457389</v>
       </c>
       <c r="B32" t="n">
         <v>99195</v>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4324,21 +4324,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dragmansbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602495</v>
+        <v>602427</v>
       </c>
       <c r="R32" t="n">
-        <v>6634554</v>
+        <v>6634739</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4370,7 +4365,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4380,12 +4375,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Blomstängel</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4411,51 +4401,65 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134457412</t>
+          <t>https://artportalen.se/Sighting/134457389</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134457414</v>
+        <v>134457412</v>
       </c>
       <c r="B33" t="n">
-        <v>98063</v>
+        <v>99195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dragmansbo, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602627</v>
+        <v>602495</v>
       </c>
       <c r="R33" t="n">
-        <v>6634611</v>
+        <v>6634554</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4487,7 +4491,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4497,7 +4501,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blomstängel</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4522,6 +4531,118 @@
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457412</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134457414</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dragmansbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>602627</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6634611</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Simtuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134457414</t>
         </is>
@@ -4561,6 +4682,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21810-2026 artfynd.xlsx
+++ b/artfynd/A 21810-2026 artfynd.xlsx
@@ -3706,7 +3706,7 @@
         <v>134457420</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
